--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -556,15 +556,13 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr"/>
+      <c r="E2" s="8" t="n">
+        <v>46</v>
+      </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -584,15 +582,13 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="8" t="n">
+        <v>225706</v>
+      </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -612,15 +608,13 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="8" t="n">
+        <v>525856</v>
+      </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -640,15 +634,13 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="8" t="n">
+        <v>266113</v>
+      </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -668,15 +660,13 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="8" t="n">
+        <v>22027092</v>
+      </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -696,15 +686,13 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="8" t="n">
+        <v>29548</v>
+      </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -724,15 +712,13 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="8" t="n">
+        <v>93194</v>
+      </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -752,15 +738,13 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="8" t="n">
+        <v>46</v>
+      </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -780,15 +764,13 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="8" t="n">
+        <v>66244</v>
+      </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -808,15 +790,13 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="8" t="n">
+        <v>46</v>
+      </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -836,15 +816,13 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="8" t="n">
+        <v>308626</v>
+      </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -864,15 +842,13 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="8" t="n">
+        <v>100519</v>
+      </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -892,15 +868,13 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="8" t="n">
+        <v>269204</v>
+      </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -920,15 +894,13 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="8" t="n">
+        <v>101840</v>
+      </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -948,15 +920,13 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="8" t="n">
+        <v>66641</v>
+      </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -976,15 +946,13 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="8" t="n">
+        <v>75481</v>
+      </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1004,15 +972,13 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="8" t="n">
+        <v>144527</v>
+      </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1032,15 +998,13 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="8" t="n">
+        <v>71677</v>
+      </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1060,15 +1024,13 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="8" t="n">
+        <v>77244</v>
+      </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1088,15 +1050,13 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="8" t="n">
+        <v>6781749</v>
+      </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1116,15 +1076,13 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="8" t="n">
+        <v>929482</v>
+      </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1144,15 +1102,13 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+      <c r="E23" s="8" t="n">
+        <v>46</v>
+      </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1172,15 +1128,13 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="8" t="n">
+        <v>96389</v>
+      </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1200,15 +1154,13 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="8" t="n">
+        <v>255212</v>
+      </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1228,15 +1180,13 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr"/>
+      <c r="E26" s="8" t="n">
+        <v>340220</v>
+      </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1256,15 +1206,13 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr"/>
+      <c r="E27" s="8" t="n">
+        <v>6598</v>
+      </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1284,15 +1232,13 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr"/>
+      <c r="E28" s="8" t="n">
+        <v>800486</v>
+      </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1312,15 +1258,13 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr"/>
+      <c r="E29" s="8" t="n">
+        <v>67940</v>
+      </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1340,15 +1284,13 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr"/>
+      <c r="E30" s="8" t="n">
+        <v>2389738</v>
+      </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1368,15 +1310,13 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr"/>
+      <c r="E31" s="8" t="n">
+        <v>333899</v>
+      </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1396,15 +1336,13 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr"/>
+      <c r="E32" s="8" t="n">
+        <v>340841</v>
+      </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1424,15 +1362,13 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr"/>
+      <c r="E33" s="8" t="n">
+        <v>171169</v>
+      </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1452,15 +1388,13 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr"/>
+      <c r="E34" s="8" t="n">
+        <v>244252</v>
+      </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1480,15 +1414,13 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr"/>
+      <c r="E35" s="8" t="n">
+        <v>428565</v>
+      </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1508,15 +1440,13 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr"/>
+      <c r="E36" s="8" t="n">
+        <v>123974</v>
+      </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1536,15 +1466,13 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr"/>
+      <c r="E37" s="8" t="n">
+        <v>778731</v>
+      </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1564,15 +1492,13 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr"/>
+      <c r="E38" s="8" t="n">
+        <v>283214</v>
+      </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1592,15 +1518,13 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr"/>
+      <c r="E39" s="8" t="n">
+        <v>732192</v>
+      </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1620,15 +1544,13 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr"/>
+      <c r="E40" s="8" t="n">
+        <v>278733</v>
+      </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1648,15 +1570,13 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr"/>
+      <c r="E41" s="8" t="n">
+        <v>109006</v>
+      </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1676,15 +1596,13 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr"/>
+      <c r="E42" s="8" t="n">
+        <v>224118</v>
+      </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1704,15 +1622,13 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr"/>
+      <c r="E43" s="8" t="n">
+        <v>242092</v>
+      </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1732,15 +1648,13 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr"/>
+      <c r="E44" s="8" t="n">
+        <v>381932</v>
+      </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1760,15 +1674,13 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr"/>
+      <c r="E45" s="8" t="n">
+        <v>113459</v>
+      </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1788,15 +1700,13 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E46" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr"/>
+      <c r="E46" s="8" t="n">
+        <v>1397760</v>
+      </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1816,15 +1726,13 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr"/>
+      <c r="E47" s="8" t="n">
+        <v>82457</v>
+      </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1844,15 +1752,13 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr"/>
+      <c r="E48" s="8" t="n">
+        <v>32256</v>
+      </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1872,15 +1778,13 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr"/>
+      <c r="E49" s="8" t="n">
+        <v>340100</v>
+      </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1900,15 +1804,13 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr"/>
+      <c r="E50" s="8" t="n">
+        <v>46</v>
+      </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1928,15 +1830,13 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr"/>
+      <c r="E51" s="8" t="n">
+        <v>1559387</v>
+      </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1956,15 +1856,13 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr"/>
+      <c r="E52" s="8" t="n">
+        <v>139317</v>
+      </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -1984,15 +1882,13 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr"/>
+      <c r="E53" s="8" t="n">
+        <v>1389397</v>
+      </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2012,15 +1908,13 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr"/>
+      <c r="E54" s="8" t="n">
+        <v>464657</v>
+      </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2040,15 +1934,13 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr"/>
+      <c r="E55" s="8" t="n">
+        <v>109006</v>
+      </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2068,15 +1960,13 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr"/>
+      <c r="E56" s="8" t="n">
+        <v>136293</v>
+      </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2096,15 +1986,13 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr"/>
+      <c r="E57" s="8" t="n">
+        <v>101040</v>
+      </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2124,15 +2012,13 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr"/>
+      <c r="E58" s="8" t="n">
+        <v>99253</v>
+      </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2152,15 +2038,13 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr"/>
+      <c r="E59" s="8" t="n">
+        <v>262604</v>
+      </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2180,15 +2064,13 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr"/>
+      <c r="E60" s="8" t="n">
+        <v>615458</v>
+      </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2208,15 +2090,13 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr"/>
+      <c r="E61" s="8" t="n">
+        <v>407459</v>
+      </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2236,15 +2116,13 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr"/>
+      <c r="E62" s="8" t="n">
+        <v>78730</v>
+      </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2264,15 +2142,13 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr"/>
+      <c r="E63" s="8" t="n">
+        <v>102597</v>
+      </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2292,15 +2168,13 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr"/>
+      <c r="E64" s="8" t="n">
+        <v>130063</v>
+      </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2320,15 +2194,13 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr"/>
+      <c r="E65" s="8" t="n">
+        <v>334057</v>
+      </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2348,15 +2220,13 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr"/>
+      <c r="E66" s="8" t="n">
+        <v>680920</v>
+      </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2376,15 +2246,13 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr"/>
+      <c r="E67" s="8" t="n">
+        <v>268458</v>
+      </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2404,15 +2272,13 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr"/>
+      <c r="E68" s="8" t="n">
+        <v>371830</v>
+      </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2432,15 +2298,13 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E69" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr"/>
+      <c r="E69" s="8" t="n">
+        <v>372060</v>
+      </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2460,15 +2324,13 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr"/>
+      <c r="E70" s="8" t="n">
+        <v>606742</v>
+      </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2488,15 +2350,13 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E71" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr"/>
+      <c r="E71" s="8" t="n">
+        <v>263854</v>
+      </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2516,15 +2376,13 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr"/>
+      <c r="E72" s="8" t="n">
+        <v>173396</v>
+      </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2544,15 +2402,13 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr"/>
+      <c r="E73" s="8" t="n">
+        <v>46</v>
+      </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2572,15 +2428,13 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr"/>
+      <c r="E74" s="8" t="n">
+        <v>46</v>
+      </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2600,15 +2454,13 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr"/>
+      <c r="E75" s="8" t="n">
+        <v>1000901</v>
+      </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2628,15 +2480,13 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr"/>
+      <c r="E76" s="8" t="n">
+        <v>2450284</v>
+      </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2656,15 +2506,13 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr"/>
+      <c r="E77" s="8" t="n">
+        <v>27358</v>
+      </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2684,15 +2532,13 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr"/>
+      <c r="E78" s="8" t="n">
+        <v>101840</v>
+      </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2712,15 +2558,13 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr"/>
+      <c r="E79" s="8" t="n">
+        <v>46</v>
+      </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2740,15 +2584,13 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr"/>
+      <c r="E80" s="8" t="n">
+        <v>201941</v>
+      </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2768,15 +2610,13 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr"/>
+      <c r="E81" s="8" t="n">
+        <v>118412</v>
+      </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2796,15 +2636,13 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr"/>
+      <c r="E82" s="8" t="n">
+        <v>436276</v>
+      </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2824,15 +2662,13 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr"/>
+      <c r="E83" s="8" t="n">
+        <v>159181</v>
+      </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2852,15 +2688,13 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr"/>
+      <c r="E84" s="8" t="n">
+        <v>963884</v>
+      </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2880,15 +2714,13 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr"/>
+      <c r="E85" s="8" t="n">
+        <v>181923</v>
+      </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2908,15 +2740,13 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr"/>
+      <c r="E86" s="8" t="n">
+        <v>196912</v>
+      </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2936,15 +2766,13 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr"/>
+      <c r="E87" s="8" t="n">
+        <v>116798</v>
+      </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2964,15 +2792,13 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E88" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr"/>
+      <c r="E88" s="8" t="n">
+        <v>184464</v>
+      </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -2992,15 +2818,13 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr"/>
+      <c r="E89" s="8" t="n">
+        <v>4767626</v>
+      </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3020,15 +2844,13 @@
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E90" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr"/>
+      <c r="E90" s="8" t="n">
+        <v>105472</v>
+      </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3048,15 +2870,13 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E91" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr"/>
+      <c r="E91" s="8" t="n">
+        <v>253823</v>
+      </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3076,15 +2896,13 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr"/>
+      <c r="E92" s="8" t="n">
+        <v>150820</v>
+      </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3104,15 +2922,13 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E93" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr"/>
+      <c r="E93" s="8" t="n">
+        <v>1987313</v>
+      </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3132,15 +2948,13 @@
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E94" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr"/>
+      <c r="E94" s="8" t="n">
+        <v>528084</v>
+      </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3160,15 +2974,13 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E95" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr"/>
+      <c r="E95" s="8" t="n">
+        <v>36718</v>
+      </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3188,15 +3000,13 @@
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E96" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr"/>
+      <c r="E96" s="8" t="n">
+        <v>46</v>
+      </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3216,15 +3026,13 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E97" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr"/>
+      <c r="E97" s="8" t="n">
+        <v>68096</v>
+      </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3244,15 +3052,13 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E98" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr"/>
+      <c r="E98" s="8" t="n">
+        <v>42496</v>
+      </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3272,15 +3078,13 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr"/>
+      <c r="E99" s="8" t="n">
+        <v>577524</v>
+      </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3300,15 +3104,13 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E100" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr"/>
+      <c r="E100" s="8" t="n">
+        <v>46</v>
+      </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3328,15 +3130,13 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E101" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr"/>
+      <c r="E101" s="8" t="n">
+        <v>242092</v>
+      </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3356,15 +3156,13 @@
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E102" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr"/>
+      <c r="E102" s="8" t="n">
+        <v>101840</v>
+      </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3384,15 +3182,13 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E103" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr"/>
+      <c r="E103" s="8" t="n">
+        <v>101840</v>
+      </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3412,15 +3208,13 @@
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E104" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr"/>
+      <c r="E104" s="8" t="n">
+        <v>67353</v>
+      </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3440,15 +3234,13 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E105" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr"/>
+      <c r="E105" s="8" t="n">
+        <v>60416</v>
+      </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3468,15 +3260,13 @@
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D106" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E106" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr"/>
+      <c r="E106" s="8" t="n">
+        <v>35308</v>
+      </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3496,15 +3286,13 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E107" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr"/>
+      <c r="E107" s="8" t="n">
+        <v>14744</v>
+      </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3524,15 +3312,13 @@
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D108" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E108" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr"/>
+      <c r="E108" s="8" t="n">
+        <v>210683</v>
+      </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3552,15 +3338,13 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D109" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E109" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr"/>
+      <c r="E109" s="8" t="n">
+        <v>46592</v>
+      </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3580,15 +3364,13 @@
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E110" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr"/>
+      <c r="E110" s="8" t="n">
+        <v>17975</v>
+      </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3608,15 +3390,13 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E111" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr"/>
+      <c r="E111" s="8" t="n">
+        <v>165064</v>
+      </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3636,15 +3416,13 @@
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D112" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E112" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr"/>
+      <c r="E112" s="8" t="n">
+        <v>74575</v>
+      </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3664,15 +3442,13 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D113" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E113" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr"/>
+      <c r="E113" s="8" t="n">
+        <v>198064</v>
+      </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3692,15 +3468,13 @@
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D114" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E114" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr"/>
+      <c r="E114" s="8" t="n">
+        <v>78401</v>
+      </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3720,15 +3494,13 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E115" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr"/>
+      <c r="E115" s="8" t="n">
+        <v>85189</v>
+      </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3748,15 +3520,13 @@
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D116" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E116" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr"/>
+      <c r="E116" s="8" t="n">
+        <v>213372</v>
+      </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3776,15 +3546,13 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E117" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr"/>
+      <c r="E117" s="8" t="n">
+        <v>29209</v>
+      </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3804,15 +3572,13 @@
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D118" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E118" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr"/>
+      <c r="E118" s="8" t="n">
+        <v>101840</v>
+      </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3832,15 +3598,13 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E119" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr"/>
+      <c r="E119" s="8" t="n">
+        <v>156466</v>
+      </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3860,15 +3624,13 @@
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D120" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E120" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr"/>
+      <c r="E120" s="8" t="n">
+        <v>50134</v>
+      </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3888,15 +3650,13 @@
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D121" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E121" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr"/>
+      <c r="E121" s="8" t="n">
+        <v>55356</v>
+      </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3916,15 +3676,13 @@
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D122" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E122" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr"/>
+      <c r="E122" s="8" t="n">
+        <v>68144</v>
+      </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3944,15 +3702,13 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D123" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E123" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr"/>
+      <c r="E123" s="8" t="n">
+        <v>79872</v>
+      </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -3972,15 +3728,13 @@
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D124" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E124" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr"/>
+      <c r="E124" s="8" t="n">
+        <v>580001</v>
+      </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4000,15 +3754,13 @@
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D125" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E125" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr"/>
+      <c r="E125" s="8" t="n">
+        <v>773471</v>
+      </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4028,15 +3780,13 @@
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D126" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E126" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr"/>
+      <c r="E126" s="8" t="n">
+        <v>14848</v>
+      </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4056,15 +3806,13 @@
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D127" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E127" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr"/>
+      <c r="E127" s="8" t="n">
+        <v>379658</v>
+      </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4084,15 +3832,13 @@
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D128" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E128" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr"/>
+      <c r="E128" s="8" t="n">
+        <v>20891207</v>
+      </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4112,15 +3858,13 @@
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D129" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E129" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr"/>
+      <c r="E129" s="8" t="n">
+        <v>159693</v>
+      </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4140,15 +3884,13 @@
       </c>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D130" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E130" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr"/>
+      <c r="E130" s="8" t="n">
+        <v>345489</v>
+      </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4168,15 +3910,13 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D131" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E131" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr"/>
+      <c r="E131" s="8" t="n">
+        <v>286761</v>
+      </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4196,15 +3936,13 @@
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D132" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E132" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr"/>
+      <c r="E132" s="8" t="n">
+        <v>299569</v>
+      </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4224,15 +3962,13 @@
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D133" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E133" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr"/>
+      <c r="E133" s="8" t="n">
+        <v>56514</v>
+      </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4252,15 +3988,13 @@
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D134" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E134" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr"/>
+      <c r="E134" s="8" t="n">
+        <v>41984</v>
+      </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4280,15 +4014,13 @@
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D135" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E135" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr"/>
+      <c r="E135" s="8" t="n">
+        <v>67072</v>
+      </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4308,15 +4040,13 @@
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D136" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E136" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr"/>
+      <c r="E136" s="8" t="n">
+        <v>32256</v>
+      </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4336,15 +4066,13 @@
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D137" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E137" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr"/>
+      <c r="E137" s="8" t="n">
+        <v>44032</v>
+      </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4364,15 +4092,13 @@
       </c>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D138" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E138" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr"/>
+      <c r="E138" s="8" t="n">
+        <v>12540</v>
+      </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4392,15 +4118,13 @@
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D139" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E139" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr"/>
+      <c r="E139" s="8" t="n">
+        <v>221083</v>
+      </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4420,15 +4144,13 @@
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D140" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E140" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr"/>
+      <c r="E140" s="8" t="n">
+        <v>40448</v>
+      </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4448,15 +4170,13 @@
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D141" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E141" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr"/>
+      <c r="E141" s="8" t="n">
+        <v>73864</v>
+      </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4476,15 +4196,13 @@
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D142" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E142" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr"/>
+      <c r="E142" s="8" t="n">
+        <v>233302</v>
+      </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4504,15 +4222,13 @@
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E143" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr"/>
+      <c r="E143" s="8" t="n">
+        <v>49164</v>
+      </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4532,15 +4248,13 @@
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D144" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E144" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr"/>
+      <c r="E144" s="8" t="n">
+        <v>190595</v>
+      </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4560,15 +4274,13 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D145" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E145" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr"/>
+      <c r="E145" s="8" t="n">
+        <v>34685</v>
+      </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4588,15 +4300,13 @@
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D146" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E146" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr"/>
+      <c r="E146" s="8" t="n">
+        <v>13994</v>
+      </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4616,15 +4326,13 @@
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D147" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E147" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr"/>
+      <c r="E147" s="8" t="n">
+        <v>847416</v>
+      </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4644,15 +4352,13 @@
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D148" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E148" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr"/>
+      <c r="E148" s="8" t="n">
+        <v>191783</v>
+      </c>
       <c r="F148" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4672,15 +4378,13 @@
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D149" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E149" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr"/>
+      <c r="E149" s="8" t="n">
+        <v>20133</v>
+      </c>
       <c r="F149" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4700,15 +4404,13 @@
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D150" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E150" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr"/>
+      <c r="E150" s="8" t="n">
+        <v>19143</v>
+      </c>
       <c r="F150" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -4728,15 +4430,13 @@
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D151" s="7" t="inlineStr">
-        <is>
-          <t>No se pudo interpretar el link/handle pegado</t>
-        </is>
-      </c>
-      <c r="E151" s="8" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr"/>
+      <c r="E151" s="8" t="n">
+        <v>146307</v>
+      </c>
       <c r="F151" s="7" t="inlineStr">
         <is>
           <t>2026-07-20</t>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4321,7 +4321,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5387,7 +5387,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5933,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5985,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6505,7 +6505,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6531,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2443,11 +2443,11 @@
       </c>
       <c r="D66" s="3" t="inlineStr"/>
       <c r="E66" s="4" t="n">
-        <v>105472</v>
+        <v>556963</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Componiendo experiencias: Un abordaje de la exigibilidad de derechos humanos con adolescentes privados de la libertad</t>
+          <t>Componiendo experiencias: un abordaje de la exigibilidad de derechos humanos con adolescentes privados de la libertad</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -4985,11 +4985,11 @@
       </c>
       <c r="D148" s="3" t="inlineStr"/>
       <c r="E148" s="4" t="n">
-        <v>4767626</v>
+        <v>592707</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7283,7 +7283,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7655,7 +7655,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8430,7 +8430,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8585,7 +8585,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9143,7 +9143,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9174,7 +9174,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9949,7 +9949,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10321,7 +10321,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10662,7 +10662,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10755,7 +10755,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10817,7 +10817,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -10972,7 +10972,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11065,7 +11065,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11375,7 +11375,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11437,7 +11437,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11596,7 +11596,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11627,7 +11627,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11751,7 +11751,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11782,7 +11782,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11906,7 +11906,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -11968,7 +11968,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12123,7 +12123,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12247,7 +12247,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12340,7 +12340,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12371,7 +12371,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12433,7 +12433,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12464,7 +12464,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12495,7 +12495,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12619,7 +12619,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>ESTUDIO DE CONFIABILIDAD Y VALIDEZ DEL INSTRUMENTO PARA EVALUAR COMPETENCIAS EN INVESTIGACIÓN (PECI)</t>
+          <t>Estudio de confiabilidad y validez del instrumento para evaluar competencias en investigación (PECI)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1234,11 +1234,11 @@
       </c>
       <c r="D27" s="3" t="inlineStr"/>
       <c r="E27" s="4" t="n">
-        <v>36718</v>
+        <v>202047</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>El Valor del Método Biográfico en una Experiencia de Aprendizaje: la Identidad en la Formación Pre-Profesional</t>
+          <t>El valor del método biográfico en una experiencia de aprendizaje : la identidad en la formación pre-profesional</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -1730,11 +1730,11 @@
       </c>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="4" t="n">
-        <v>68096</v>
+        <v>428390</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>HISTORIA DE LA PSICOLOGÍA FRANCESA EN CÓRDOBA: ANÁLISIS CUANTITATIVO DE REFERENCIAS A AUTORES FRANCESES EN TESIS DE MEDICINA (1896 ? 1918)</t>
+          <t>Historia de la psicología francesa en córdoba : análisis cuantitativo de referencias a autores franceses en tesis de medicina (1896-1918)</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -4365,11 +4365,11 @@
       </c>
       <c r="D128" s="3" t="inlineStr"/>
       <c r="E128" s="4" t="n">
-        <v>528084</v>
+        <v>1035178</v>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>La línea de investigación argentina Ecolocación Humana: diálogos interdisciplinares en el estudio de fenómenos de (audio) percepción-acción sin claves visuales.</t>
+          <t>La línea de investigación argentina ecolocación humana : diálogos interdisciplinares en el estudio de fenómenos de (audio) percepción-acción sin claves visuales</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7283,7 +7283,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7624,7 +7624,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7655,7 +7655,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7810,7 +7810,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8089,7 +8089,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8430,7 +8430,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8585,7 +8585,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9143,7 +9143,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9174,7 +9174,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9422,7 +9422,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9794,7 +9794,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9949,7 +9949,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10228,7 +10228,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10321,7 +10321,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10383,7 +10383,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10414,7 +10414,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10631,7 +10631,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10662,7 +10662,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10755,7 +10755,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10817,7 +10817,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -10972,7 +10972,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11065,7 +11065,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11158,7 +11158,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11375,7 +11375,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11437,7 +11437,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11468,7 +11468,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11534,7 +11534,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11596,7 +11596,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11627,7 +11627,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11751,7 +11751,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11782,7 +11782,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11906,7 +11906,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -11968,7 +11968,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12123,7 +12123,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12247,7 +12247,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12309,7 +12309,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12340,7 +12340,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12371,7 +12371,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12433,7 +12433,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12464,7 +12464,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12495,7 +12495,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12619,7 +12619,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12650,7 +12650,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -2996,16 +2996,18 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr"/>
-      <c r="E84" s="4" t="n">
-        <v>173396</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3036,7 +3038,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3067,7 +3069,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3098,7 +3100,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3129,7 +3131,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3160,7 +3162,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3191,7 +3193,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3222,7 +3224,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3253,7 +3255,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3284,7 +3286,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3315,7 +3317,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3346,7 +3348,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3377,7 +3379,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3408,7 +3410,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3439,7 +3441,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3470,7 +3472,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3501,7 +3503,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3532,7 +3534,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3563,7 +3565,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3594,7 +3596,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3625,7 +3627,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3656,7 +3658,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3687,7 +3689,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3718,7 +3720,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3749,7 +3751,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3780,7 +3782,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3811,7 +3813,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3842,7 +3844,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3873,7 +3875,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3904,7 +3906,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3935,7 +3937,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3966,7 +3968,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -3997,7 +3999,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4028,7 +4030,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4059,7 +4061,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4090,7 +4092,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4121,7 +4123,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4152,7 +4154,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4183,7 +4185,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4214,7 +4216,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4245,7 +4247,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4276,7 +4278,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4307,7 +4309,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4338,7 +4340,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4369,7 +4371,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4400,7 +4402,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4431,7 +4433,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4462,7 +4464,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4493,7 +4495,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4524,7 +4526,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4555,7 +4557,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4586,7 +4588,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4617,7 +4619,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4648,7 +4650,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4679,7 +4681,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4710,7 +4712,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4741,7 +4743,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4772,7 +4774,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4803,7 +4805,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4834,7 +4836,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4865,7 +4867,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4896,7 +4898,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4927,7 +4929,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4958,7 +4960,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -4989,7 +4991,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5020,7 +5022,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5051,7 +5053,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5082,7 +5084,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5113,7 +5115,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5144,7 +5146,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5175,7 +5177,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5206,7 +5208,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5237,7 +5239,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5268,7 +5270,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5299,7 +5301,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5330,7 +5332,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5361,7 +5363,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5392,7 +5394,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5423,7 +5425,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5454,7 +5456,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5485,7 +5487,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5516,7 +5518,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5547,7 +5549,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5578,7 +5580,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5609,7 +5611,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5640,7 +5642,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5671,7 +5673,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5702,7 +5704,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5733,7 +5735,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5764,7 +5766,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5795,7 +5797,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5826,7 +5828,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5857,7 +5859,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5888,7 +5890,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5919,7 +5921,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5950,7 +5952,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -5981,7 +5983,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6012,7 +6014,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6043,7 +6045,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6074,7 +6076,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6105,7 +6107,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6136,7 +6138,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6167,7 +6169,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6198,7 +6200,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6229,7 +6231,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6260,7 +6262,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6291,7 +6293,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6322,7 +6324,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6353,7 +6355,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6384,7 +6386,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6415,7 +6417,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6446,7 +6448,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6477,7 +6479,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6508,7 +6510,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6539,7 +6541,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6570,7 +6572,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6601,7 +6603,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6632,7 +6634,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6663,7 +6665,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6694,7 +6696,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6725,7 +6727,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6756,7 +6758,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6787,7 +6789,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6818,7 +6820,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6849,7 +6851,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6880,7 +6882,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6911,7 +6913,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6942,7 +6944,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -6973,7 +6975,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7004,7 +7006,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7035,7 +7037,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7066,7 +7068,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7097,7 +7099,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7128,7 +7130,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7159,7 +7161,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7190,7 +7192,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7221,7 +7223,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7252,7 +7254,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7283,7 +7285,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7314,7 +7316,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7345,7 +7347,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7376,7 +7378,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7407,7 +7409,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7438,7 +7440,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7469,7 +7471,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7500,7 +7502,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7531,7 +7533,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7562,7 +7564,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7593,7 +7595,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7624,7 +7626,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7655,7 +7657,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7686,7 +7688,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7717,7 +7719,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7748,7 +7750,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7779,7 +7781,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7810,7 +7812,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7841,7 +7843,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7872,7 +7874,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7903,7 +7905,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7934,7 +7936,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -7965,7 +7967,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -7996,7 +7998,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8027,7 +8029,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8058,7 +8060,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8089,7 +8091,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8120,7 +8122,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8151,7 +8153,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8182,7 +8184,7 @@
       </c>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8213,7 +8215,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8244,7 +8246,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8275,7 +8277,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8306,7 +8308,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8337,7 +8339,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8368,7 +8370,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8399,7 +8401,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8430,7 +8432,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8461,7 +8463,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8492,7 +8494,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8523,7 +8525,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8554,7 +8556,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8585,7 +8587,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8616,7 +8618,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8647,7 +8649,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8678,7 +8680,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8709,7 +8711,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8740,7 +8742,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8771,7 +8773,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8802,7 +8804,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8833,7 +8835,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8864,7 +8866,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8895,7 +8897,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8926,7 +8928,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -8957,7 +8959,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -8988,7 +8990,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9019,7 +9021,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9050,7 +9052,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9081,7 +9083,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9112,7 +9114,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9143,7 +9145,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9174,7 +9176,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9205,7 +9207,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9236,7 +9238,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9267,7 +9269,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9298,7 +9300,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9329,7 +9331,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9360,7 +9362,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9391,7 +9393,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9422,7 +9424,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9453,7 +9455,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9484,7 +9486,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9515,7 +9517,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9546,7 +9548,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9577,7 +9579,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9608,7 +9610,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9639,7 +9641,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9670,7 +9672,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9701,7 +9703,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9732,7 +9734,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9763,7 +9765,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9794,7 +9796,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9825,7 +9827,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9856,7 +9858,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9887,7 +9889,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9918,7 +9920,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9949,7 +9951,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -9980,7 +9982,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10011,7 +10013,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10042,7 +10044,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10073,7 +10075,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10104,7 +10106,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10135,7 +10137,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10166,7 +10168,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10197,7 +10199,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10228,7 +10230,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10259,7 +10261,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10290,7 +10292,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10321,7 +10323,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10352,7 +10354,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10383,7 +10385,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10414,7 +10416,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10445,7 +10447,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10476,7 +10478,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10507,7 +10509,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10538,7 +10540,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10569,7 +10571,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10600,7 +10602,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10631,7 +10633,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10662,7 +10664,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10693,7 +10695,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10724,7 +10726,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10755,7 +10757,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10786,7 +10788,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10817,7 +10819,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10848,7 +10850,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10879,7 +10881,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10910,7 +10912,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10941,7 +10943,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -10972,7 +10974,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11003,7 +11005,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11034,7 +11036,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11065,7 +11067,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11096,7 +11098,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11127,7 +11129,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11158,7 +11160,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11189,7 +11191,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11220,7 +11222,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11251,7 +11253,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11282,7 +11284,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11313,7 +11315,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11344,7 +11346,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11375,7 +11377,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11406,7 +11408,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11437,7 +11439,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11468,7 +11470,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11503,7 +11505,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11534,7 +11536,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11565,7 +11567,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11596,7 +11598,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11627,7 +11629,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11658,7 +11660,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11689,7 +11691,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11720,7 +11722,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11751,7 +11753,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11782,7 +11784,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11813,7 +11815,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11844,7 +11846,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11875,7 +11877,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11906,7 +11908,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11937,7 +11939,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -11968,7 +11970,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -11999,7 +12001,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12030,7 +12032,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12061,7 +12063,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12092,7 +12094,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12123,7 +12125,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12154,7 +12156,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12185,7 +12187,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12216,7 +12218,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12247,7 +12249,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12278,7 +12280,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12309,7 +12311,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12340,7 +12342,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12371,7 +12373,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12402,7 +12404,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12433,7 +12435,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12464,7 +12466,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12495,7 +12497,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12526,7 +12528,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12557,7 +12559,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12588,7 +12590,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12619,7 +12621,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12650,7 +12652,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12681,7 +12683,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3007,7 +3007,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9145,7 +9145,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -9982,7 +9982,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10416,7 +10416,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10912,7 +10912,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11408,7 +11408,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11908,7 +11908,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3007,7 +3007,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9145,7 +9145,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -9982,7 +9982,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10416,7 +10416,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10912,7 +10912,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11408,7 +11408,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11908,7 +11908,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3007,7 +3007,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9145,7 +9145,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -9982,7 +9982,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10416,7 +10416,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10912,7 +10912,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11408,7 +11408,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11908,7 +11908,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Competencias para investigar en estudiantes de la Carrera de Psicología y su posible relación con la formación curricular</t>
+          <t>Competencias para investigar en estudiantes de la carrera de psicología y su posible relación con la formación curricular</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>UNA APROXIMACION A LA CONCEPTUALIZACION DE LA HISTERIA EN SU RELACION CON LA POSICION SEXUADA, DESDE LA PERSPECTIVA DEL PSICOANALISIS</t>
+          <t>Una aproximación a la conceptualización de la histeria en su relación con la posición sexuada, desde la perspectiva del psicoanálisis</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Evaluación de competencias de investigación en estudiantes de Psicología</t>
+          <t>Evaluación de competencias de investigación en estudiantes de psicología</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3007,7 +3007,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Escala de Actitudes Ambientales Ecocéntricas y Antropocéntricas: análisis psicométrico en una muestra de ciudadanos cordobeses.</t>
+          <t>Escala de actitudes ambientales ecocéntricas y antropocéntricas : análisis psicométrico en una muestra de ciudadanos cordobeses</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Docosahexaenoic Acid Upregulates Iduna Expression in the Ischemic Penumbra and Protects Rat Brains against Focal Ischemia</t>
+          <t>Docosahexaenoic acid upreg</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9145,7 +9145,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -9982,7 +9982,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10416,7 +10416,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10912,7 +10912,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11408,7 +11408,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11908,7 +11908,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Bullying y ciberbullying: Su relación con estrategias de afrontamiento en adolescentes escolarizados.</t>
+          <t>Bullying y ciberbullying : su relación con estrategias de afrontamiento en adolescentes escolarizados</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1327,11 +1327,11 @@
       </c>
       <c r="D30" s="3" t="inlineStr"/>
       <c r="E30" s="4" t="n">
-        <v>42496</v>
+        <v>224771</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3007,7 +3007,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Envidia benigna y maligna: experiencia y patrones valorativos</t>
+          <t>Envidia benigna y maligna : experiencia y patrones valorativos</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Procesos socioculturales y construcciones de género: saberes académicos y prácticas nativas?</t>
+          <t>Procesos socioculturales y construcciones de género : saberes académicos y prácticas nativas</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>De los juegos de la vida a los juegos de la muerte en la adolescencia: Estrategias de abordaje para la construcción de espacios de subjetivación, lazo social y ciudadanía</t>
+          <t>De los juegos de la vida a los juegos de la muerte en la adolescencia : estrategias de abordaje para la construcción de espacios de subjetivación, lazo social y ciudadanía</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -5018,11 +5018,11 @@
       </c>
       <c r="D149" s="3" t="inlineStr"/>
       <c r="E149" s="4" t="n">
-        <v>6781749</v>
+        <v>1209099</v>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5704,7 +5704,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5766,7 +5766,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6417,7 +6417,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6479,7 +6479,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8122,7 +8122,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8308,7 +8308,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8897,7 +8897,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9145,7 +9145,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9424,7 +9424,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9610,7 +9610,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -9982,7 +9982,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10106,7 +10106,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10416,7 +10416,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10602,7 +10602,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10912,7 +10912,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11408,7 +11408,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11908,7 +11908,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11939,7 +11939,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12125,7 +12125,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12435,7 +12435,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12559,7 +12559,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1105,16 +1105,18 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="4" t="n">
-        <v>32256</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1145,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1176,7 +1178,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1193,7 +1195,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Personality, age, and antisocial peers: Relationships with violent and non-violent crimes</t>
+          <t>Personality, age, and antisocial peers : relationships with violent and non-violent crimes</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1207,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1238,7 +1240,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1269,7 +1271,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1300,7 +1302,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1331,7 +1333,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1362,7 +1364,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1393,7 +1395,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1424,7 +1426,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1455,7 +1457,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1486,7 +1488,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1517,7 +1519,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1534,7 +1536,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Crisis familiares y estrategias para enfrentarlas.</t>
+          <t>Crisis familiares y estrategias para enfrentarlas</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1548,7 +1550,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1579,7 +1581,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1610,7 +1612,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1641,7 +1643,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1658,7 +1660,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>PREVALENCIA DE TRASTORNOS NEURÓTICOS EN CONSULTANTES DEL PRIMER NIVEL DE ATENCIÓN DE UN BARRIO DE CÓRDOBA.</t>
+          <t>Prevalencia de trastornos neuróticos en consultantes del primer nivel de atención de un barrio de Córdoba</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -1672,7 +1674,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1703,7 +1705,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1734,7 +1736,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1765,7 +1767,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1796,7 +1798,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1827,7 +1829,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1858,7 +1860,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1889,7 +1891,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1920,7 +1922,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1951,7 +1953,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1982,7 +1984,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2013,7 +2015,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2044,7 +2046,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2075,7 +2077,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2106,7 +2108,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2137,7 +2139,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2168,7 +2170,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2199,7 +2201,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2230,7 +2232,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2261,7 +2263,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2292,7 +2294,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2323,7 +2325,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2354,7 +2356,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2385,7 +2387,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2416,7 +2418,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2447,7 +2449,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2478,7 +2480,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2509,7 +2511,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2540,7 +2542,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2571,7 +2573,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2602,7 +2604,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2633,7 +2635,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2664,7 +2666,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2695,7 +2697,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2726,7 +2728,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2757,7 +2759,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2788,7 +2790,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2819,7 +2821,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2850,7 +2852,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2881,7 +2883,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2912,7 +2914,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2943,7 +2945,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2974,7 +2976,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3007,7 +3009,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3038,7 +3040,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3069,7 +3071,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3100,7 +3102,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3131,7 +3133,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3162,7 +3164,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3193,7 +3195,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3224,7 +3226,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3255,7 +3257,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3286,7 +3288,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3317,7 +3319,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3348,7 +3350,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3379,7 +3381,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3410,7 +3412,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3441,7 +3443,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3472,7 +3474,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3503,7 +3505,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3534,7 +3536,7 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3565,7 +3567,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3596,7 +3598,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3618,16 +3620,18 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr"/>
-      <c r="E104" s="4" t="n">
-        <v>263854</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3658,7 +3662,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3689,7 +3693,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3720,7 +3724,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3751,7 +3755,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3782,7 +3786,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3813,7 +3817,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3844,7 +3848,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3875,7 +3879,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3906,7 +3910,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3937,7 +3941,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3968,7 +3972,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -3999,7 +4003,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4030,7 +4034,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4061,7 +4065,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4083,16 +4087,18 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr"/>
-      <c r="E119" s="4" t="n">
-        <v>371830</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4123,7 +4129,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4154,7 +4160,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4185,7 +4191,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4216,7 +4222,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4247,7 +4253,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4278,7 +4284,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4309,7 +4315,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4340,7 +4346,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4371,7 +4377,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4402,7 +4408,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4433,7 +4439,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4455,16 +4461,18 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr"/>
-      <c r="E131" s="4" t="n">
-        <v>606742</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4495,7 +4503,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4526,7 +4534,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4557,7 +4565,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4588,7 +4596,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4619,7 +4627,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4650,7 +4658,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4681,7 +4689,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4712,7 +4720,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4743,7 +4751,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4774,7 +4782,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4805,7 +4813,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4836,7 +4844,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4867,7 +4875,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4898,7 +4906,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4929,7 +4937,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4960,7 +4968,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -4991,7 +4999,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5022,7 +5030,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5053,7 +5061,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5084,7 +5092,7 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5115,7 +5123,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5146,7 +5154,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5177,7 +5185,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5208,7 +5216,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5239,7 +5247,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5270,7 +5278,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5301,7 +5309,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5332,7 +5340,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5363,7 +5371,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5394,7 +5402,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5425,7 +5433,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5456,7 +5464,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5487,7 +5495,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5518,7 +5526,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5549,7 +5557,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5580,7 +5588,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5611,7 +5619,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5642,7 +5650,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5673,7 +5681,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5704,7 +5712,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5735,7 +5743,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5766,7 +5774,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5797,7 +5805,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5828,7 +5836,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5859,7 +5867,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5890,7 +5898,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5921,7 +5929,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5952,7 +5960,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -5983,7 +5991,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6014,7 +6022,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6045,7 +6053,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6076,7 +6084,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6107,7 +6115,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6138,7 +6146,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6169,7 +6177,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6200,7 +6208,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6231,7 +6239,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6262,7 +6270,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6293,7 +6301,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6324,7 +6332,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6355,7 +6363,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6386,7 +6394,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6417,7 +6425,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6448,7 +6456,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6479,7 +6487,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6510,7 +6518,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6541,7 +6549,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6572,7 +6580,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6603,7 +6611,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6634,7 +6642,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6665,7 +6673,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6696,7 +6704,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6727,7 +6735,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6758,7 +6766,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6789,7 +6797,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6820,7 +6828,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6851,7 +6859,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6882,7 +6890,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6913,7 +6921,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6944,7 +6952,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -6975,7 +6983,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7006,7 +7014,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7037,7 +7045,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7068,7 +7076,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7099,7 +7107,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7130,7 +7138,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7161,7 +7169,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7192,7 +7200,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7223,7 +7231,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7254,7 +7262,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7285,7 +7293,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7316,7 +7324,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7347,7 +7355,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7378,7 +7386,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7409,7 +7417,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7440,7 +7448,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7471,7 +7479,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7502,7 +7510,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7533,7 +7541,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7564,7 +7572,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7595,7 +7603,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7626,7 +7634,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7657,7 +7665,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7688,7 +7696,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7719,7 +7727,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7750,7 +7758,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7781,7 +7789,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7812,7 +7820,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7843,7 +7851,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7874,7 +7882,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7905,7 +7913,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7936,7 +7944,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -7967,7 +7975,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -7998,7 +8006,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8029,7 +8037,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8060,7 +8068,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8091,7 +8099,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8122,7 +8130,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8153,7 +8161,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8184,7 +8192,7 @@
       </c>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8215,7 +8223,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8246,7 +8254,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8277,7 +8285,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8308,7 +8316,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8339,7 +8347,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8370,7 +8378,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8401,7 +8409,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8432,7 +8440,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8463,7 +8471,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8494,7 +8502,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8525,7 +8533,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8556,7 +8564,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8587,7 +8595,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8618,7 +8626,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8649,7 +8657,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8680,7 +8688,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8711,7 +8719,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8742,7 +8750,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8773,7 +8781,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8804,7 +8812,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8835,7 +8843,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8866,7 +8874,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8897,7 +8905,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8928,7 +8936,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -8959,7 +8967,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -8990,7 +8998,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9021,7 +9029,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9052,7 +9060,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9083,7 +9091,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9114,7 +9122,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9145,7 +9153,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9176,7 +9184,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9207,7 +9215,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9238,7 +9246,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9269,7 +9277,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9300,7 +9308,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9331,7 +9339,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9362,7 +9370,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9393,7 +9401,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9424,7 +9432,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9455,7 +9463,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9486,7 +9494,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9517,7 +9525,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9548,7 +9556,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9579,7 +9587,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9610,7 +9618,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9641,7 +9649,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9672,7 +9680,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9703,7 +9711,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9734,7 +9742,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9765,7 +9773,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9796,7 +9804,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9827,7 +9835,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9858,7 +9866,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9889,7 +9897,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9920,7 +9928,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9951,7 +9959,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -9982,7 +9990,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10013,7 +10021,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10044,7 +10052,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10075,7 +10083,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10106,7 +10114,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10137,7 +10145,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10168,7 +10176,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10199,7 +10207,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10230,7 +10238,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10261,7 +10269,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10292,7 +10300,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10323,7 +10331,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10354,7 +10362,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10385,7 +10393,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10416,7 +10424,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10447,7 +10455,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10478,7 +10486,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10509,7 +10517,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10540,7 +10548,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10571,7 +10579,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10602,7 +10610,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10633,7 +10641,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10664,7 +10672,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10695,7 +10703,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10726,7 +10734,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10757,7 +10765,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10788,7 +10796,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10819,7 +10827,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10850,7 +10858,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10881,7 +10889,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10912,7 +10920,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10943,7 +10951,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -10974,7 +10982,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11005,7 +11013,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11036,7 +11044,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11067,7 +11075,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11098,7 +11106,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11129,7 +11137,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11160,7 +11168,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11191,7 +11199,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11222,7 +11230,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11253,7 +11261,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11284,7 +11292,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11315,7 +11323,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11346,7 +11354,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11377,7 +11385,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11408,7 +11416,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11439,7 +11447,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11470,7 +11478,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11505,7 +11513,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11536,7 +11544,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11567,7 +11575,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11598,7 +11606,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11629,7 +11637,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11660,7 +11668,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11691,7 +11699,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11722,7 +11730,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11753,7 +11761,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11784,7 +11792,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11815,7 +11823,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11846,7 +11854,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11877,7 +11885,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11908,7 +11916,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11939,7 +11947,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -11970,7 +11978,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12001,7 +12009,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12032,7 +12040,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12063,7 +12071,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12094,7 +12102,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12125,7 +12133,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12156,7 +12164,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12187,7 +12195,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12218,7 +12226,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12249,7 +12257,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12280,7 +12288,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12311,7 +12319,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12342,7 +12350,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12373,7 +12381,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12404,7 +12412,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12435,7 +12443,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12466,7 +12474,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12497,7 +12505,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12528,7 +12536,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12559,7 +12567,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12590,7 +12598,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12621,7 +12629,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12652,7 +12660,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12683,7 +12691,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Personas en situación de calle institucionalizadas y subjetivación política: Entre nombres y líneas de fuga frente a los dispositivos de poder en una hospedería de la ciudad de Córdoba.</t>
+          <t>Personas en situación de calle institucionalizadas y subjetivación política : entre nombres y líneas de fuga frente a los dispositivos de poder en una hospedería de la ciudad de Córdoba</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1231,16 +1231,18 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="4" t="n">
-        <v>202047</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1271,7 +1273,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1302,7 +1304,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1333,7 +1335,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1364,7 +1366,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1381,7 +1383,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>LA PARTICIPACIÓN CULTURAL EN ADOLESCENTES Y JÓVENES DE DIFERENTES AMBITOS REGIONALES. SOBRE LA CREATIVIDAD, LA SOLIDARIDAD Y LA INCLUSIÓN EDUCATIVA</t>
+          <t>La participación cultural en adolescentes y jóvenes de diferentes ámbitos regionales : sobre</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1395,7 +1397,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1426,7 +1428,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1457,7 +1459,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1488,7 +1490,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1519,7 +1521,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1550,7 +1552,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1581,7 +1583,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1603,16 +1605,18 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="4" t="n">
-        <v>66641</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1643,7 +1647,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1674,7 +1678,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1705,7 +1709,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1727,16 +1731,18 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="4" t="n">
-        <v>428390</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1767,7 +1773,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1798,7 +1804,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1829,7 +1835,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1860,7 +1866,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1882,16 +1888,18 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="4" t="n">
-        <v>75481</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1922,7 +1930,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1953,7 +1961,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1984,7 +1992,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2015,7 +2023,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2046,7 +2054,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2077,7 +2085,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2099,16 +2107,18 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="4" t="n">
-        <v>93194</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2130,16 +2140,18 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="4" t="n">
-        <v>96389</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2170,7 +2182,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2201,7 +2213,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2232,7 +2244,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2263,7 +2275,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2294,7 +2306,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2325,7 +2337,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2356,7 +2368,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2387,7 +2399,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2418,7 +2430,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2440,16 +2452,18 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr"/>
-      <c r="E66" s="4" t="n">
-        <v>556963</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2480,7 +2494,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2511,7 +2525,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2542,7 +2556,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2573,7 +2587,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2595,16 +2609,18 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="4" t="n">
-        <v>118412</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2635,7 +2651,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2666,7 +2682,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2697,7 +2713,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2728,7 +2744,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2759,7 +2775,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2790,7 +2806,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2812,16 +2828,18 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr"/>
-      <c r="E78" s="4" t="n">
-        <v>150820</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2852,7 +2870,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2883,7 +2901,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2914,7 +2932,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2931,7 +2949,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Riesgo de adicción en la vejez: la automedicación y el policonsumo medicamentoso en mayores</t>
+          <t>Riesgo de adicción en la</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -2945,7 +2963,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2976,7 +2994,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3009,7 +3027,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3040,7 +3058,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3062,16 +3080,18 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr"/>
-      <c r="E86" s="4" t="n">
-        <v>184464</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3102,7 +3122,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3133,7 +3153,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3164,7 +3184,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3195,7 +3215,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3226,7 +3246,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3243,7 +3263,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>ESTRATEGIAS FAMILIARES PARA ENFRENTAR LA HOSPITALIZACION DE NIÑOS</t>
+          <t>Estrategias familiares para enfrentar la hospitalización de niños</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -3257,7 +3277,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3288,7 +3308,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3319,7 +3339,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3350,7 +3370,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3372,16 +3392,18 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr"/>
-      <c r="E96" s="4" t="n">
-        <v>225706</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3412,7 +3434,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3443,7 +3465,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3474,7 +3496,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3505,7 +3527,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3527,16 +3549,18 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr"/>
-      <c r="E101" s="4" t="n">
-        <v>253823</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3567,7 +3591,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3598,7 +3622,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3631,7 +3655,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3653,16 +3677,18 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr"/>
-      <c r="E105" s="4" t="n">
-        <v>266113</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3693,7 +3719,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3724,7 +3750,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3755,7 +3781,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3786,7 +3812,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3817,7 +3843,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3848,7 +3874,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3879,7 +3905,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3910,7 +3936,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3941,7 +3967,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3972,7 +3998,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -4003,7 +4029,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4034,7 +4060,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4065,7 +4091,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4098,7 +4124,7 @@
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4129,7 +4155,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4160,7 +4186,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4191,7 +4217,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4222,7 +4248,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4253,7 +4279,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4284,7 +4310,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4315,7 +4341,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4346,7 +4372,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4368,16 +4394,18 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr"/>
-      <c r="E128" s="4" t="n">
-        <v>1035178</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4408,7 +4436,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4439,7 +4467,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4472,7 +4500,7 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4503,7 +4531,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4534,7 +4562,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4565,7 +4593,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4596,7 +4624,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4627,7 +4655,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4658,7 +4686,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4689,7 +4717,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4720,7 +4748,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4751,7 +4779,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4782,7 +4810,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4813,7 +4841,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4844,7 +4872,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4875,7 +4903,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4897,16 +4925,18 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr"/>
-      <c r="E145" s="4" t="n">
-        <v>1987313</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4937,7 +4967,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4968,7 +4998,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -4990,16 +5020,18 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="inlineStr"/>
-      <c r="E148" s="4" t="n">
-        <v>592707</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5030,7 +5062,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5061,7 +5093,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5083,16 +5115,18 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr"/>
-      <c r="E151" s="4" t="n">
-        <v>1138887</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5123,7 +5157,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5154,7 +5188,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5185,7 +5219,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5216,7 +5250,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5247,7 +5281,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5278,7 +5312,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5309,7 +5343,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5340,7 +5374,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5371,7 +5405,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5402,7 +5436,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5433,7 +5467,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5464,7 +5498,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5495,7 +5529,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5526,7 +5560,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5557,7 +5591,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5588,7 +5622,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5619,7 +5653,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5650,7 +5684,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5681,7 +5715,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5712,7 +5746,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5743,7 +5777,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5774,7 +5808,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5805,7 +5839,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5836,7 +5870,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5867,7 +5901,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5898,7 +5932,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5929,7 +5963,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5960,7 +5994,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -5991,7 +6025,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6022,7 +6056,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6053,7 +6087,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6084,7 +6118,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6115,7 +6149,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6146,7 +6180,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6177,7 +6211,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6208,7 +6242,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6239,7 +6273,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6270,7 +6304,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6301,7 +6335,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6332,7 +6366,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6363,7 +6397,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6394,7 +6428,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6425,7 +6459,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6456,7 +6490,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6487,7 +6521,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6518,7 +6552,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6549,7 +6583,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6580,7 +6614,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6611,7 +6645,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6642,7 +6676,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6673,7 +6707,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6704,7 +6738,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6735,7 +6769,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6766,7 +6800,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6797,7 +6831,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6828,7 +6862,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6859,7 +6893,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6890,7 +6924,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6921,7 +6955,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6952,7 +6986,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -6983,7 +7017,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7014,7 +7048,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7045,7 +7079,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7076,7 +7110,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7107,7 +7141,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7138,7 +7172,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7169,7 +7203,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7200,7 +7234,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7231,7 +7265,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7262,7 +7296,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7293,7 +7327,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7324,7 +7358,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7355,7 +7389,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7386,7 +7420,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7417,7 +7451,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7448,7 +7482,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7479,7 +7513,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7510,7 +7544,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7541,7 +7575,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7572,7 +7606,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7603,7 +7637,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7634,7 +7668,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7665,7 +7699,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7696,7 +7730,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7727,7 +7761,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7758,7 +7792,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7789,7 +7823,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7820,7 +7854,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7851,7 +7885,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7882,7 +7916,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7913,7 +7947,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7944,7 +7978,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -7975,7 +8009,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -8006,7 +8040,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8037,7 +8071,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8068,7 +8102,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8099,7 +8133,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8130,7 +8164,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8161,7 +8195,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8183,16 +8217,18 @@
       </c>
       <c r="C251" s="6" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D251" s="6" t="inlineStr"/>
-      <c r="E251" s="6" t="n">
-        <v>237387</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D251" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E251" s="6" t="inlineStr"/>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8223,7 +8259,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8254,7 +8290,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8285,7 +8321,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8316,7 +8352,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8347,7 +8383,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8378,7 +8414,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8409,7 +8445,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8440,7 +8476,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8471,7 +8507,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8502,7 +8538,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8533,7 +8569,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8564,7 +8600,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8595,7 +8631,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8626,7 +8662,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8657,7 +8693,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8688,7 +8724,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8719,7 +8755,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8750,7 +8786,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8781,7 +8817,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8812,7 +8848,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8843,7 +8879,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8874,7 +8910,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8905,7 +8941,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8936,7 +8972,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -8967,7 +9003,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -8998,7 +9034,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9029,7 +9065,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9060,7 +9096,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9091,7 +9127,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9122,7 +9158,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9153,7 +9189,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9184,7 +9220,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9215,7 +9251,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9246,7 +9282,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9277,7 +9313,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9308,7 +9344,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9339,7 +9375,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9370,7 +9406,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9401,7 +9437,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9432,7 +9468,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9463,7 +9499,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9494,7 +9530,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9525,7 +9561,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9556,7 +9592,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9587,7 +9623,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9618,7 +9654,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9649,7 +9685,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9680,7 +9716,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9711,7 +9747,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9742,7 +9778,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9773,7 +9809,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9804,7 +9840,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9835,7 +9871,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9866,7 +9902,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9897,7 +9933,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9928,7 +9964,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9959,7 +9995,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -9990,7 +10026,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10021,7 +10057,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10052,7 +10088,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10083,7 +10119,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10114,7 +10150,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10145,7 +10181,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10176,7 +10212,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10207,7 +10243,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10238,7 +10274,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10269,7 +10305,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10300,7 +10336,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10331,7 +10367,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10362,7 +10398,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10393,7 +10429,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10424,7 +10460,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10455,7 +10491,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10486,7 +10522,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10517,7 +10553,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10548,7 +10584,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10579,7 +10615,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10610,7 +10646,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10641,7 +10677,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10672,7 +10708,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10703,7 +10739,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10734,7 +10770,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10765,7 +10801,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10796,7 +10832,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10827,7 +10863,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10858,7 +10894,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10889,7 +10925,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10920,7 +10956,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10951,7 +10987,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -10982,7 +11018,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11013,7 +11049,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11044,7 +11080,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11075,7 +11111,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11106,7 +11142,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11137,7 +11173,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11168,7 +11204,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11199,7 +11235,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11230,7 +11266,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11261,7 +11297,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11292,7 +11328,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11323,7 +11359,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11354,7 +11390,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11385,7 +11421,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11416,7 +11452,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11447,7 +11483,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11478,7 +11514,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11513,7 +11549,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11544,7 +11580,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11575,7 +11611,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11606,7 +11642,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11637,7 +11673,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11668,7 +11704,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11699,7 +11735,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11730,7 +11766,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11761,7 +11797,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11792,7 +11828,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11823,7 +11859,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11854,7 +11890,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11885,7 +11921,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11916,7 +11952,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11947,7 +11983,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -11978,7 +12014,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12009,7 +12045,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12040,7 +12076,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12071,7 +12107,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12102,7 +12138,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12133,7 +12169,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12164,7 +12200,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12195,7 +12231,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12226,7 +12262,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12257,7 +12293,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12288,7 +12324,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12319,7 +12355,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12350,7 +12386,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12381,7 +12417,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12412,7 +12448,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12443,7 +12479,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12474,7 +12510,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12505,7 +12541,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12536,7 +12572,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12567,7 +12603,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12598,7 +12634,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12629,7 +12665,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12660,7 +12696,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12691,7 +12727,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1242,7 +1242,7 @@
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1742,7 +1742,7 @@
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1899,7 +1899,7 @@
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2118,7 +2118,7 @@
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2620,7 +2620,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2839,7 +2839,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3027,7 +3027,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3091,7 +3091,7 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3403,7 +3403,7 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3560,7 +3560,7 @@
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3655,7 +3655,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3688,7 +3688,7 @@
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4124,7 +4124,7 @@
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4405,7 +4405,7 @@
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4500,7 +4500,7 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4936,7 +4936,7 @@
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -5031,7 +5031,7 @@
       <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5126,7 +5126,7 @@
       <c r="E151" s="4" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8228,7 +8228,7 @@
       <c r="E251" s="6" t="inlineStr"/>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1242,7 +1242,7 @@
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1742,7 +1742,7 @@
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1899,7 +1899,7 @@
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2118,7 +2118,7 @@
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2620,7 +2620,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2839,7 +2839,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3027,7 +3027,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3091,7 +3091,7 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3403,7 +3403,7 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3560,7 +3560,7 @@
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3655,7 +3655,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3688,7 +3688,7 @@
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4124,7 +4124,7 @@
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4405,7 +4405,7 @@
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4500,7 +4500,7 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4936,7 +4936,7 @@
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -5031,7 +5031,7 @@
       <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5126,7 +5126,7 @@
       <c r="E151" s="4" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8228,7 +8228,7 @@
       <c r="E251" s="6" t="inlineStr"/>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -914,7 +914,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Medios de Comunicación, discursos barriales y estrategias de prevención de violencia. estudio de caso en Barrio Marqués Anexo, Córdoba, caital</t>
+          <t>Medios de comunicación, discursos barriales y estrategias de prevención de violencia. estudio de caso en barrio Marqués Anexo, Córdoba Capital</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -924,11 +924,11 @@
       </c>
       <c r="D17" s="3" t="inlineStr"/>
       <c r="E17" s="4" t="n">
-        <v>17975</v>
+        <v>261720</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1242,7 +1242,7 @@
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1742,7 +1742,7 @@
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1899,7 +1899,7 @@
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2118,7 +2118,7 @@
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2620,7 +2620,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2839,7 +2839,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Riesgo de adicción en la</t>
+          <t>Riesgo de adicción en la vejez: la automedicación y el policonsumo medicamentoso en mayores</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3027,7 +3027,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3091,7 +3091,7 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3403,7 +3403,7 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3560,7 +3560,7 @@
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3655,7 +3655,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3688,7 +3688,7 @@
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4124,7 +4124,7 @@
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4405,7 +4405,7 @@
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4500,7 +4500,7 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4936,7 +4936,7 @@
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -5031,7 +5031,7 @@
       <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5126,7 +5126,7 @@
       <c r="E151" s="4" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8228,7 +8228,7 @@
       <c r="E251" s="6" t="inlineStr"/>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Los estudios experimentales de la percepción en Argentina a mediados del siglo XX. La UNSL, el CIAL y el LIS</t>
+          <t>Los estudios experimentales de la percepción en Argentina a mediados del siglo XX</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1048,11 +1048,11 @@
       </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="4" t="n">
-        <v>29209</v>
+        <v>304400</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1242,7 +1242,7 @@
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1393,11 +1393,11 @@
       </c>
       <c r="D32" s="3" t="inlineStr"/>
       <c r="E32" s="4" t="n">
-        <v>46592</v>
+        <v>300666</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>El olor de la leche materna en el fortalecimiento del vinculo mama-bebé prematuro</t>
+          <t>El olor de la leche materna en el fortalecimiento del vínculo mamá-bebé prematuro</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1742,7 +1742,7 @@
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1899,7 +1899,7 @@
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Desafíos para reconstruir Demandas Organizacionales en las PPP. Experiencias de Practicantes y Supervisores</t>
+          <t>Desafíos para reconstruir demandas organizacionales en las PPP : experiencias de practicantes y supervisores</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Formar(nos) en investigación cualitativa. Estrategias y reflexiones a partir de una experiencia de posgrado en Córdoba</t>
+          <t>Formar(nos) en investigación cualitativa : estrategias y reflexiones a partir de una experiencia de posgrado en Córdoba</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>CONSIDERACIONES PARA LA REALIZACIÓN DE ENTREVISTAS EN INVESTIGACIÓN HISTÓRICO-CUALITATIVA. PRIMERAS EXPERIENCIAS COMO ENTREVISTADOR DE ALUMNOS DE LA FACULTAD DE PSICOLOGÍA (UNC).</t>
+          <t>Consideraciones para la realización de entrevistas en investigación histórico-cualitativa : primeras experiencias como entrevistador de alumnos de la Facultad de Psicología (UNC)</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2118,7 +2118,7 @@
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Arrepentimiento y decepción asociados a las decisiones en el Juego del Ultimátum</t>
+          <t>Arrepentimiento y decepción asociados a las decisiones en el juego del ultimátum</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Una experiencia clínica en el abordaje de la toxicomanía: la posición de la mujer, pareja del toxicómano, en el sostenimiento de su adicción</t>
+          <t>Una experiencia clínica en el abordaje de la toxicomanía : la posición de</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2620,7 +2620,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2839,7 +2839,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Posturas docentes en la promoción de la salud y la convivencia en la escuela. Aprendiendo de apuestas pedagógicas instituyentes en la ciudad de Córdoba</t>
+          <t>Posturas docentes en la promoción de la salud y la convivencia en la escuela : aprendiendo de apuestas pedagógicas instituyentes en la ciudad de Córdoba</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -2866,11 +2866,11 @@
       </c>
       <c r="D79" s="3" t="inlineStr"/>
       <c r="E79" s="4" t="n">
-        <v>156466</v>
+        <v>580949</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Riesgo de adicción en la vejez: la automedicación y el policonsumo medicamentoso en mayores</t>
+          <t>Riesgo de adicción en la vejez : la automedicación y el policonsumo medicamentoso en mayores</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3027,7 +3027,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3091,7 +3091,7 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3403,7 +3403,7 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3560,7 +3560,7 @@
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3655,7 +3655,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3688,7 +3688,7 @@
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4124,7 +4124,7 @@
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4405,7 +4405,7 @@
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4500,7 +4500,7 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4936,7 +4936,7 @@
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -5031,7 +5031,7 @@
       <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Articulación entre UNC y escuelas Secundarias Públicas. Experiencias y desafieos en la construcción de una universidad más inclusiva</t>
+          <t>Articulación entre UNC y escuelas secundarias públicas : experiencias y desafíos en la construcción de una universidad más inclusiva</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5126,7 +5126,7 @@
       <c r="E151" s="4" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8228,7 +8228,7 @@
       <c r="E251" s="6" t="inlineStr"/>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>El sentido ético del rol del psicólogo educacional en una experiencia de reinvención de lo escolar desde la Pedagogía hospitalaria</t>
+          <t>El sentido ético del rol del psicólogo educacional en una experiencia de reinvención de lo escolar desde la pedagogía hospitalaria</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1242,7 +1242,7 @@
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1548,11 +1548,11 @@
       </c>
       <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="4" t="n">
-        <v>60416</v>
+        <v>252367</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1742,7 +1742,7 @@
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>SIMPOSIO: NUEVOS DERECHOS CIVILES EN LA ARGENTINA. UNA PERSPECTIVA DESDE EL PSICOANÁLISIS.</t>
+          <t>Nuevos derechos civiles en la Argentina : una perspectiva desde el psicoanálisis</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1899,7 +1899,7 @@
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2019,11 +2019,11 @@
       </c>
       <c r="D52" s="3" t="inlineStr"/>
       <c r="E52" s="4" t="n">
-        <v>79872</v>
+        <v>342222</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2118,7 +2118,7 @@
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2620,7 +2620,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>"La entrevista de autoconfrontación: un dispositivo de análisis para el estudio de la construcción de autoridad en el marco de la relación pedagógica"</t>
+          <t>La entrevista de autoconfrontación: un dispositivo de análisis para el estudio de la construcción de autoridad en el marco de la relación pedagógica</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2839,7 +2839,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Aportes de la Antropología al abordaje de la violencia contra las mujeres en el ámbito del ejercicio profesional del psicólogo.</t>
+          <t>Aportes de la antropología al abordaje de la violencia contra las mujeres en el ámbito del ejercicio profesional del psicólogo</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3027,7 +3027,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3091,7 +3091,7 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Rasgos Complejos y Rendimiento Académico: Contribución de los Rasgos de Personalidad, Creencias de Autoeficacia e Intereses</t>
+          <t>Rasgos complejos y rendimiento académico : contribución de los rasgos de personalidad, creencias de autoeficacia e intereses</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3403,7 +3403,7 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3560,7 +3560,7 @@
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3655,7 +3655,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3688,7 +3688,7 @@
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Violencias de Género: Construcción de Subjetividades Masculinas en contextos de Globalización</t>
+          <t>Violencias de género : construcción de subjetividades masculinas en contextos de globalización</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4124,7 +4124,7 @@
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4405,7 +4405,7 @@
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4500,7 +4500,7 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Use of Novelty as a way of Modulating cSNC expression: Implications of the Adrenergic System</t>
+          <t>Use of novelty as a way of modulating cSNC expression : implications of the adrenergic system</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4936,7 +4936,7 @@
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -5031,7 +5031,7 @@
       <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5089,11 +5089,11 @@
       </c>
       <c r="D150" s="3" t="inlineStr"/>
       <c r="E150" s="4" t="n">
-        <v>20891207</v>
+        <v>96231</v>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5126,7 +5126,7 @@
       <c r="E151" s="4" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8228,7 +8228,7 @@
       <c r="E251" s="6" t="inlineStr"/>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1242,7 +1242,7 @@
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1742,7 +1742,7 @@
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1899,7 +1899,7 @@
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2118,7 +2118,7 @@
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2620,7 +2620,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2839,7 +2839,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3027,7 +3027,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3091,7 +3091,7 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3403,7 +3403,7 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3560,7 +3560,7 @@
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3655,7 +3655,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3688,7 +3688,7 @@
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4124,7 +4124,7 @@
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4405,7 +4405,7 @@
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4500,7 +4500,7 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4936,7 +4936,7 @@
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -5031,7 +5031,7 @@
       <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5126,7 +5126,7 @@
       <c r="E151" s="4" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8228,7 +8228,7 @@
       <c r="E251" s="6" t="inlineStr"/>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1242,7 +1242,7 @@
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1742,7 +1742,7 @@
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1899,7 +1899,7 @@
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2118,7 +2118,7 @@
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2620,7 +2620,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2839,7 +2839,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3027,7 +3027,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3091,7 +3091,7 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3403,7 +3403,7 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3560,7 +3560,7 @@
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3655,7 +3655,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3688,7 +3688,7 @@
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4124,7 +4124,7 @@
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4405,7 +4405,7 @@
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4500,7 +4500,7 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4936,7 +4936,7 @@
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -5031,7 +5031,7 @@
       <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5126,7 +5126,7 @@
       <c r="E151" s="4" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8228,7 +8228,7 @@
       <c r="E251" s="6" t="inlineStr"/>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1242,7 +1242,7 @@
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1742,7 +1742,7 @@
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1899,7 +1899,7 @@
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2118,7 +2118,7 @@
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2620,7 +2620,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2839,7 +2839,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3027,7 +3027,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3091,7 +3091,7 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3403,7 +3403,7 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3560,7 +3560,7 @@
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3655,7 +3655,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3688,7 +3688,7 @@
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4124,7 +4124,7 @@
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4405,7 +4405,7 @@
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4500,7 +4500,7 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4936,7 +4936,7 @@
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -5031,7 +5031,7 @@
       <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5126,7 +5126,7 @@
       <c r="E151" s="4" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8228,7 +8228,7 @@
       <c r="E251" s="6" t="inlineStr"/>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -945,7 +945,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Representaciones de los docentes sobre los niños designados en sus aulas como dispersos o hiperactivosasociadas al uso indebido de sustancias psicoactivas de adolescentes en riesgo socioeducativo e implementación de estrategias preventivas</t>
+          <t>Representaciones de los docentes sobre los niños designados en sus aulas como dispersos o hiperactivos : asociadas al uso indebido de sustancias psicoactivas de adolescentes en riesgo socioeducativo e implementación de estrategias preventivas</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -955,11 +955,11 @@
       </c>
       <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="4" t="n">
-        <v>19143</v>
+        <v>111970</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Promoviendo espacios saludables. Espacio de escucha y contención en la Escuela Mariano Moreno.</t>
+          <t>Promoviendo espacios saludables : espacio de escucha y contención en la Escuela Mariano Moreno</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -986,11 +986,11 @@
       </c>
       <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="4" t="n">
-        <v>20133</v>
+        <v>117085</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>La Expresión Creativa en el Dibujo Libre de Niños/as Cordobeses</t>
+          <t>La expresión creativa en el dibujo libre de niños/as cordobeses</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1174,11 +1174,11 @@
       </c>
       <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="4" t="n">
-        <v>34685</v>
+        <v>622567</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1242,7 +1242,7 @@
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Evaluación de las prácticas preprofesionales del contexto jurídico de la carrera de Psicología de la UNC. Opinión de los egresados sobre facilitadores y obstáculos del aprendizaje</t>
+          <t>Evaluación de las prácticas preprofesionales del contexto jurídico de la carrera de Psicología de la UNC : opinión de los egresados sobre facilitadores y obstáculos del aprendizaje</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1269,11 +1269,11 @@
       </c>
       <c r="D28" s="3" t="inlineStr"/>
       <c r="E28" s="4" t="n">
-        <v>40448</v>
+        <v>132766</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Formas de trabajo en la gestión y Calidad de vida laboral</t>
+          <t>Formas de trabajo en la gestión y calidad de vida laboral</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1300,11 +1300,11 @@
       </c>
       <c r="D29" s="3" t="inlineStr"/>
       <c r="E29" s="4" t="n">
-        <v>41984</v>
+        <v>435203</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Comunicación Libre: Estrategias tempranas para una articulación oportuna entre el nivel inicial y el nivel primario.</t>
+          <t>Comunicación libre : estrategias tempranas para una articulación oportuna entre el nivel inicial y el nivel primario</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Promoviendo vínculos saludables. Espacio de escucha y contención en la Escuela  Mariano Moreno.</t>
+          <t>Promoviendo vínculos saludables : espacio de escucha y contención en la Escuela Mariano Moreno</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Sustentabilidad e innovación en Pymes</t>
+          <t>Sustentabilidad e innovación en pymes</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1643,11 +1643,11 @@
       </c>
       <c r="D40" s="3" t="inlineStr"/>
       <c r="E40" s="4" t="n">
-        <v>67072</v>
+        <v>614223</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1742,7 +1742,7 @@
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>¿QUIEN COMANDA LA HIPERMODERNIDAD? EL SÚPER YO Y SUS AVATARES EN LA ACTUALIDAD.</t>
+          <t>¿Quien comanda la hipermodernidad? : el super yo y sus avatares en la actualidad</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1899,7 +1899,7 @@
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2118,7 +2118,7 @@
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2620,7 +2620,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>La entrevista de autoconfrontación: un dispositivo de análisis para el estudio de la construcción de autoridad en el marco de la relación pedagógica</t>
+          <t>La entrevista de autoconfrontación : un dispositivo de análisis para el estudio de la construcción de autoridad en el marco de la relación pedagógica</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2839,7 +2839,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3027,7 +3027,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3091,7 +3091,7 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Revisión de estudios previos sobre consumo de alcohol en ratas por efecto de Separación Materna</t>
+          <t>Revisión de estudios previos sobre consumo de alcohol en ratas por efecto de separación materna</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3403,7 +3403,7 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Verdad cifrada, manera por la que el pasado recibe la impresión de una actualidad más reciente</t>
+          <t>Verdad cifrada : manera por la que el pasado recibe la impresión de una actualidad más reciente</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3560,7 +3560,7 @@
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3655,7 +3655,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3688,7 +3688,7 @@
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Género, participación y vida cotidiana: etnografiando experiencias de encuentros entre mujeres</t>
+          <t>Género, participación y vida cotidiana : etnografiando experiencias de encuentros entre mujeres</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>?Procesos socioculturales  construcciones de género: saberes académicos y prácticas nativas?</t>
+          <t>Procesos socioculturales construcciones de género : saberes académicos y prácticas nativas</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4124,7 +4124,7 @@
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4405,7 +4405,7 @@
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4500,7 +4500,7 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4936,7 +4936,7 @@
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -5031,7 +5031,7 @@
       <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5126,7 +5126,7 @@
       <c r="E151" s="4" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8228,7 +8228,7 @@
       <c r="E251" s="6" t="inlineStr"/>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -893,11 +893,11 @@
       </c>
       <c r="D16" s="3" t="inlineStr"/>
       <c r="E16" s="4" t="n">
-        <v>14848</v>
+        <v>29783</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1242,7 +1242,7 @@
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Trastornos mentales según variables socidemográficas en un centro de salud de un barrio en emergencia sanitaria</t>
+          <t>Trastornos mentales según variables sociodemográficas en un centro de salud de un barrio en emergencia sanitaria</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1742,7 +1742,7 @@
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1899,7 +1899,7 @@
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2118,7 +2118,7 @@
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2620,7 +2620,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2839,7 +2839,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3027,7 +3027,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3091,7 +3091,7 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>AN ANIMAL MODEL OF PRENATAL ALCOHOL EFFECTS ON LEARNING AND ALCOHOL INTAKE</t>
+          <t>An animal model of prenatal alcohol effects on learning and alcohol intake</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>SIMPOSIO: DESARROLLOS ACTUALES EN INVESTIGACIÓN DEL FORO DE CÁTEDRAS DE ÉTICA Y DEONTOLOGÍA PROFESIONAL PARTE I y II.</t>
+          <t>Simposio: desarrollos actuales en investigación del Foro de Cátedras de Ética y Deontología Profesional parte I y II</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3403,7 +3403,7 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3560,7 +3560,7 @@
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3655,7 +3655,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3688,7 +3688,7 @@
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4124,7 +4124,7 @@
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4405,7 +4405,7 @@
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4500,7 +4500,7 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4936,7 +4936,7 @@
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -5031,7 +5031,7 @@
       <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5126,7 +5126,7 @@
       <c r="E151" s="4" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8228,7 +8228,7 @@
       <c r="E251" s="6" t="inlineStr"/>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1242,7 +1242,7 @@
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1742,7 +1742,7 @@
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1899,7 +1899,7 @@
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2118,7 +2118,7 @@
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2620,7 +2620,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2839,7 +2839,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3027,7 +3027,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3091,7 +3091,7 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3403,7 +3403,7 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3560,7 +3560,7 @@
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3655,7 +3655,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3688,7 +3688,7 @@
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4124,7 +4124,7 @@
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4405,7 +4405,7 @@
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4500,7 +4500,7 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>CONSUMO DE ALCOHOL Y CONDUCCIÓN: REVISIÓN DE LOS PRINCIPALES RESULTADOS EN ESTUDIOS CON SIMULADORES DE MANEJO</t>
+          <t>Consumo de alcohol y conducción: revisión de los principales resultados en estudios con simuladores de manejo</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4936,7 +4936,7 @@
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -5031,7 +5031,7 @@
       <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5126,7 +5126,7 @@
       <c r="E151" s="4" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8228,7 +8228,7 @@
       <c r="E251" s="6" t="inlineStr"/>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1242,7 +1242,7 @@
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1742,7 +1742,7 @@
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1899,7 +1899,7 @@
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2118,7 +2118,7 @@
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2620,7 +2620,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2839,7 +2839,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3027,7 +3027,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3091,7 +3091,7 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3403,7 +3403,7 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3560,7 +3560,7 @@
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3655,7 +3655,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3688,7 +3688,7 @@
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4124,7 +4124,7 @@
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4217,7 +4217,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4405,7 +4405,7 @@
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4500,7 +4500,7 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4936,7 +4936,7 @@
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -5031,7 +5031,7 @@
       <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -5126,7 +5126,7 @@
       <c r="E151" s="4" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G151" s="2" t="n"/>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G152" s="2" t="n"/>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G153" s="2" t="n"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G154" s="2" t="n"/>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G155" s="2" t="n"/>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G156" s="2" t="n"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G157" s="2" t="n"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G158" s="2" t="n"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G159" s="2" t="n"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G160" s="2" t="n"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G161" s="2" t="n"/>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G162" s="2" t="n"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G163" s="2" t="n"/>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G166" s="2" t="n"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G167" s="2" t="n"/>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G171" s="2" t="n"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G172" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G173" s="2" t="n"/>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G174" s="2" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G175" s="2" t="n"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G176" s="2" t="n"/>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G177" s="2" t="n"/>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G178" s="2" t="n"/>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G179" s="2" t="n"/>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G180" s="2" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G182" s="2" t="n"/>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G183" s="2" t="n"/>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G184" s="2" t="n"/>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G185" s="2" t="n"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G186" s="2" t="n"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G188" s="2" t="n"/>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G189" s="2" t="n"/>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G190" s="2" t="n"/>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G191" s="2" t="n"/>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G192" s="2" t="n"/>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -6521,7 +6521,7 @@
       </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G196" s="2" t="n"/>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G201" s="2" t="n"/>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G202" s="2" t="n"/>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G203" s="2" t="n"/>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G204" s="2" t="n"/>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G205" s="2" t="n"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G206" s="2" t="n"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G207" s="2" t="n"/>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G208" s="2" t="n"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G209" s="2" t="n"/>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G210" s="2" t="n"/>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G211" s="2" t="n"/>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G212" s="2" t="n"/>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G213" s="2" t="n"/>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G214" s="2" t="n"/>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G215" s="2" t="n"/>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G216" s="2" t="n"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G217" s="2" t="n"/>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G218" s="2" t="n"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G219" s="2" t="n"/>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G220" s="2" t="n"/>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G221" s="2" t="n"/>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G222" s="2" t="n"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G223" s="2" t="n"/>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G224" s="2" t="n"/>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G225" s="2" t="n"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G226" s="2" t="n"/>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G227" s="2" t="n"/>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G228" s="2" t="n"/>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G229" s="2" t="n"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G230" s="2" t="n"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G231" s="2" t="n"/>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G232" s="2" t="n"/>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="F233" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G233" s="2" t="n"/>
@@ -7699,7 +7699,7 @@
       </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G234" s="2" t="n"/>
@@ -7730,7 +7730,7 @@
       </c>
       <c r="F235" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G235" s="2" t="n"/>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G236" s="2" t="n"/>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G237" s="2" t="n"/>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G238" s="2" t="n"/>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G239" s="2" t="n"/>
@@ -7885,7 +7885,7 @@
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G240" s="2" t="n"/>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G241" s="2" t="n"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G242" s="2" t="n"/>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="F243" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G243" s="2" t="n"/>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G244" s="2" t="n"/>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G245" s="2" t="n"/>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G246" s="2" t="n"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G247" s="2" t="n"/>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G248" s="2" t="n"/>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G249" s="2" t="n"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G250" s="2" t="n"/>
@@ -8228,7 +8228,7 @@
       <c r="E251" s="6" t="inlineStr"/>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G251" s="2" t="n"/>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G252" s="2" t="n"/>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G253" s="2" t="n"/>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G254" s="2" t="n"/>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G255" s="2" t="n"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G256" s="2" t="n"/>
@@ -8414,7 +8414,7 @@
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G257" s="2" t="n"/>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G258" s="2" t="n"/>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="F259" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G259" s="2" t="n"/>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G260" s="2" t="n"/>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F261" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G261" s="2" t="n"/>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G262" s="2" t="n"/>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G263" s="2" t="n"/>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G264" s="2" t="n"/>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G265" s="2" t="n"/>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G266" s="2" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G267" s="2" t="n"/>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G268" s="2" t="n"/>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G269" s="2" t="n"/>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G270" s="2" t="n"/>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G271" s="2" t="n"/>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G272" s="2" t="n"/>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G273" s="2" t="n"/>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G274" s="2" t="n"/>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G275" s="2" t="n"/>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G276" s="2" t="n"/>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G277" s="2" t="n"/>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G278" s="2" t="n"/>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G279" s="2" t="n"/>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G280" s="2" t="n"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G281" s="2" t="n"/>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G282" s="2" t="n"/>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G283" s="2" t="n"/>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G284" s="2" t="n"/>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G285" s="2" t="n"/>
@@ -9313,7 +9313,7 @@
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G286" s="2" t="n"/>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G287" s="2" t="n"/>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G288" s="2" t="n"/>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G289" s="2" t="n"/>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G290" s="2" t="n"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G291" s="2" t="n"/>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G292" s="2" t="n"/>
@@ -9530,7 +9530,7 @@
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G293" s="2" t="n"/>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="F294" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G294" s="2" t="n"/>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G295" s="2" t="n"/>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G296" s="2" t="n"/>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G297" s="2" t="n"/>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G298" s="2" t="n"/>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G299" s="2" t="n"/>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G300" s="2" t="n"/>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G301" s="2" t="n"/>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G302" s="2" t="n"/>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G303" s="2" t="n"/>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="F304" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G304" s="2" t="n"/>
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G305" s="2" t="n"/>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F306" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G306" s="2" t="n"/>
@@ -9964,7 +9964,7 @@
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G307" s="2" t="n"/>
@@ -9995,7 +9995,7 @@
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G308" s="2" t="n"/>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G309" s="2" t="n"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="F310" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G310" s="2" t="n"/>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G311" s="2" t="n"/>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G312" s="2" t="n"/>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G313" s="2" t="n"/>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G314" s="2" t="n"/>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G315" s="2" t="n"/>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G316" s="2" t="n"/>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="F317" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G317" s="2" t="n"/>
@@ -10305,7 +10305,7 @@
       </c>
       <c r="F318" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G318" s="2" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="F319" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G319" s="2" t="n"/>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="F320" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G320" s="2" t="n"/>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="F321" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G321" s="2" t="n"/>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="F322" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G322" s="2" t="n"/>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="F323" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G323" s="2" t="n"/>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="F324" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G324" s="2" t="n"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="F325" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G325" s="2" t="n"/>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="F326" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G326" s="2" t="n"/>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="F327" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G327" s="2" t="n"/>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="F328" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G328" s="2" t="n"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="F329" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G329" s="2" t="n"/>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="F330" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G330" s="2" t="n"/>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F331" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G331" s="2" t="n"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G332" s="2" t="n"/>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="F333" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G333" s="2" t="n"/>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="F334" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G334" s="2" t="n"/>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="F335" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G335" s="2" t="n"/>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="F336" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G336" s="2" t="n"/>
@@ -10894,7 +10894,7 @@
       </c>
       <c r="F337" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G337" s="2" t="n"/>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="F338" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G338" s="2" t="n"/>
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F339" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G339" s="2" t="n"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="F340" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G340" s="2" t="n"/>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="F341" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G341" s="2" t="n"/>
@@ -11049,7 +11049,7 @@
       </c>
       <c r="F342" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G342" s="2" t="n"/>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="F343" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G343" s="2" t="n"/>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="F344" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G344" s="2" t="n"/>
@@ -11142,7 +11142,7 @@
       </c>
       <c r="F345" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G345" s="2" t="n"/>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="F346" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G346" s="2" t="n"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="F347" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G347" s="2" t="n"/>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="F348" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G348" s="2" t="n"/>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="F349" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G349" s="2" t="n"/>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="F350" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G350" s="2" t="n"/>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G351" s="2" t="n"/>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="F352" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G352" s="2" t="n"/>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="F353" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G353" s="2" t="n"/>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="F354" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G354" s="2" t="n"/>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="F355" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G355" s="2" t="n"/>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="F356" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G356" s="2" t="n"/>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="F357" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G357" s="2" t="n"/>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="F358" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G358" s="2" t="n"/>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F359" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G359" s="2" t="n"/>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="F360" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G360" s="2" t="n"/>
@@ -11642,7 +11642,7 @@
       </c>
       <c r="F361" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G361" s="2" t="n"/>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="F362" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G362" s="2" t="n"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F363" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G363" s="2" t="n"/>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F364" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G364" s="2" t="n"/>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="F365" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G365" s="2" t="n"/>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="F366" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G366" s="2" t="n"/>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="F367" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G367" s="2" t="n"/>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F368" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G368" s="2" t="n"/>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F369" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G369" s="2" t="n"/>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="F370" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G370" s="2" t="n"/>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="F371" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G371" s="2" t="n"/>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="F372" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G372" s="2" t="n"/>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="F373" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G373" s="2" t="n"/>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="F374" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G374" s="2" t="n"/>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="F375" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G375" s="2" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="F376" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G376" s="2" t="n"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G377" s="2" t="n"/>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="F378" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G378" s="2" t="n"/>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F379" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G379" s="2" t="n"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="F380" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G380" s="2" t="n"/>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="F381" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G381" s="2" t="n"/>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="F382" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G382" s="2" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="F383" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G383" s="2" t="n"/>
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F384" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G384" s="2" t="n"/>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="F385" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G385" s="2" t="n"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="F386" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G386" s="2" t="n"/>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="F387" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G387" s="2" t="n"/>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="F388" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G388" s="2" t="n"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F389" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G389" s="2" t="n"/>
@@ -12541,7 +12541,7 @@
       </c>
       <c r="F390" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G390" s="2" t="n"/>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F391" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G391" s="2" t="n"/>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="F392" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G392" s="2" t="n"/>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="F393" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G393" s="2" t="n"/>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="F394" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G394" s="2" t="n"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="F395" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G395" s="2" t="n"/>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="F396" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G396" s="2" t="n"/>

--- a/reportes/entradas_a_revisar.xlsx
+++ b/reportes/entradas_a_revisar.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -494,7 +494,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -587,7 +587,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -649,7 +649,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G11" s="2" t="n"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G13" s="2" t="n"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G14" s="2" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G15" s="2" t="n"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G16" s="2" t="n"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G17" s="2" t="n"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G18" s="2" t="n"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G19" s="2" t="n"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G20" s="2" t="n"/>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G21" s="2" t="n"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G22" s="2" t="n"/>
@@ -1116,7 +1116,7 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G23" s="2" t="n"/>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -1242,7 +1242,7 @@
       <c r="E27" s="4" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G27" s="2" t="n"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G30" s="2" t="n"/>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G33" s="2" t="n"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G35" s="2" t="n"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G37" s="2" t="n"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G38" s="2" t="n"/>
@@ -1616,7 +1616,7 @@
       <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G40" s="2" t="n"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G41" s="2" t="n"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G42" s="2" t="n"/>
@@ -1742,7 +1742,7 @@
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G43" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G45" s="2" t="n"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -1899,7 +1899,7 @@
       <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G48" s="2" t="n"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G49" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G50" s="2" t="n"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G51" s="2" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G54" s="2" t="n"/>
@@ -2118,7 +2118,7 @@
       <c r="E55" s="4" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G55" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
       <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G56" s="2" t="n"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G57" s="2" t="n"/>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G58" s="2" t="n"/>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G60" s="2" t="n"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G64" s="2" t="n"/>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G65" s="2" t="n"/>
@@ -2463,7 +2463,7 @@
       <c r="E66" s="4" t="inlineStr"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G66" s="2" t="n"/>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G67" s="2" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G68" s="2" t="n"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G69" s="2" t="n"/>
@@ -2578,16 +2578,18 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr"/>
-      <c r="E70" s="4" t="n">
-        <v>116798</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G70" s="2" t="n"/>
@@ -2620,7 +2622,7 @@
       <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G71" s="2" t="n"/>
@@ -2651,7 +2653,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G72" s="2" t="n"/>
@@ -2682,7 +2684,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -2713,7 +2715,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G74" s="2" t="n"/>
@@ -2744,7 +2746,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -2775,7 +2777,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G76" s="2" t="n"/>
@@ -2806,7 +2808,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G77" s="2" t="n"/>
@@ -2839,7 +2841,7 @@
       <c r="E78" s="4" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G78" s="2" t="n"/>
@@ -2870,7 +2872,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G79" s="2" t="n"/>
@@ -2892,16 +2894,18 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr"/>
-      <c r="E80" s="4" t="n">
-        <v>159181</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -2932,7 +2936,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G81" s="2" t="n"/>
@@ -2963,7 +2967,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G82" s="2" t="n"/>
@@ -2994,7 +2998,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G83" s="2" t="n"/>
@@ -3027,7 +3031,7 @@
       <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G84" s="2" t="n"/>
@@ -3058,7 +3062,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G85" s="2" t="n"/>
@@ -3091,7 +3095,7 @@
       <c r="E86" s="4" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G86" s="2" t="n"/>
@@ -3122,7 +3126,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G87" s="2" t="n"/>
@@ -3153,7 +3157,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G88" s="2" t="n"/>
@@ -3175,16 +3179,18 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr"/>
-      <c r="E89" s="4" t="n">
-        <v>196912</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr"/>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G89" s="2" t="n"/>
@@ -3215,7 +3221,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G90" s="2" t="n"/>
@@ -3246,7 +3252,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G91" s="2" t="n"/>
@@ -3277,7 +3283,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -3308,7 +3314,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G93" s="2" t="n"/>
@@ -3339,7 +3345,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G94" s="2" t="n"/>
@@ -3370,7 +3376,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -3403,7 +3409,7 @@
       <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G96" s="2" t="n"/>
@@ -3434,7 +3440,7 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G97" s="2" t="n"/>
@@ -3465,7 +3471,7 @@
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G98" s="2" t="n"/>
@@ -3487,16 +3493,18 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr"/>
-      <c r="E99" s="4" t="n">
-        <v>242092</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr"/>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G99" s="2" t="n"/>
@@ -3527,7 +3535,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G100" s="2" t="n"/>
@@ -3560,7 +3568,7 @@
       <c r="E101" s="4" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G101" s="2" t="n"/>
@@ -3591,7 +3599,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G102" s="2" t="n"/>
@@ -3622,7 +3630,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G103" s="2" t="n"/>
@@ -3655,7 +3663,7 @@
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G104" s="2" t="n"/>
@@ -3688,7 +3696,7 @@
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G105" s="2" t="n"/>
@@ -3719,7 +3727,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -3750,7 +3758,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -3781,7 +3789,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -3812,7 +3820,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G109" s="2" t="n"/>
@@ -3843,7 +3851,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G110" s="2" t="n"/>
@@ -3874,7 +3882,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G111" s="2" t="n"/>
@@ -3905,7 +3913,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G112" s="2" t="n"/>
@@ -3936,7 +3944,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G113" s="2" t="n"/>
@@ -3967,7 +3975,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G114" s="2" t="n"/>
@@ -3998,7 +4006,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G115" s="2" t="n"/>
@@ -4029,7 +4037,7 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G116" s="2" t="n"/>
@@ -4060,7 +4068,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G117" s="2" t="n"/>
@@ -4091,7 +4099,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G118" s="2" t="n"/>
@@ -4124,7 +4132,7 @@
       <c r="E119" s="4" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G119" s="2" t="n"/>
@@ -4155,7 +4163,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G120" s="2" t="n"/>
@@ -4186,7 +4194,7 @@
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G121" s="2" t="n"/>
@@ -4217,7 +4225,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G122" s="2" t="n"/>
@@ -4248,7 +4256,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G123" s="2" t="n"/>
@@ -4279,7 +4287,7 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -4301,16 +4309,18 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr"/>
-      <c r="E125" s="4" t="n">
-        <v>436276</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G125" s="2" t="n"/>
@@ -4341,7 +4351,7 @@
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G126" s="2" t="n"/>
@@ -4372,7 +4382,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -4405,7 +4415,7 @@
       <c r="E128" s="4" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -4427,16 +4437,18 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr"/>
-      <c r="E129" s="4" t="n">
-        <v>577524</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr"/>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -4467,7 +4479,7 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -4500,7 +4512,7 @@
       <c r="E131" s="4" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G131" s="2" t="n"/>
@@ -4531,7 +4543,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G132" s="2" t="n"/>
@@ -4562,7 +4574,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G133" s="2" t="n"/>
@@ -4593,7 +4605,7 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G134" s="2" t="n"/>
@@ -4624,7 +4636,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G135" s="2" t="n"/>
@@ -4655,7 +4667,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G136" s="2" t="n"/>
@@ -4686,7 +4698,7 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G137" s="2" t="n"/>
@@ -4717,7 +4729,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G138" s="2" t="n"/>
@@ -4748,7 +4760,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G139" s="2" t="n"/>
@@ -4770,16 +4782,18 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr"/>
-      <c r="E140" s="4" t="n">
-        <v>963884</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falló la consulta a RDU: HTTP Error 500: </t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr"/>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G140" s="2" t="n"/>
@@ -4810,7 +4824,7 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G141" s="2" t="n"/>
@@ -4841,7 +4855,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G142" s="2" t="n"/>
@@ -4872,7 +4886,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G143" s="2" t="n"/>
@@ -4903,7 +4917,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G144" s="2" t="n"/>
@@ -4936,7 +4950,7 @@
       <c r="E145" s="4" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G145" s="2" t="n"/>
@@ -4967,7 +4981,7 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G146" s="2" t="n"/>
@@ -4998,7 +5012,7 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G147" s="2" t="n"/>
@@ -5031,7 +5045,7 @@
       <c r="E148" s="4" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G148" s="2" t="n"/>
@@ -5053,16 +5067,18 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr"/>
-      <c r="E149" s="4" t="n">
-        <v>1209099</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+    